--- a/templateExport.xlsx
+++ b/templateExport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\New folder\crmHanhChinhNhanSu\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nghia\Desktop\temp\blockchainHC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D3A9238-D882-432B-9A84-7D47EB72F773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22616EFE-7417-4970-BF11-5BD8B8298238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27720" yWindow="3570" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -20,67 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="72">
-  <si>
-    <t>HN</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>Dai hoc</t>
-  </si>
-  <si>
-    <t>Doc than</t>
-  </si>
-  <si>
-    <t>VCB</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Nhan Vien 2</t>
-  </si>
-  <si>
-    <t>03/01/2024</t>
-  </si>
-  <si>
-    <t>POS02</t>
-  </si>
-  <si>
-    <t>DEP02</t>
-  </si>
-  <si>
-    <t>nu</t>
-  </si>
-  <si>
-    <t>03/01/1990</t>
-  </si>
-  <si>
-    <t>03/01/2010</t>
-  </si>
-  <si>
-    <t>Dia chi TT 2</t>
-  </si>
-  <si>
-    <t>Dia chi TTam 2</t>
-  </si>
-  <si>
-    <t>nhanvien2@company.com</t>
-  </si>
-  <si>
-    <t>nhanvien2@gmail.com</t>
-  </si>
-  <si>
-    <t>0900000002</t>
-  </si>
-  <si>
-    <t>7000000002</t>
-  </si>
-  <si>
-    <t>Nhan Vien 100</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="61">
   <si>
     <t>STT</t>
   </si>
@@ -970,16 +910,43 @@
     </r>
   </si>
   <si>
-    <t>ma001</t>
-  </si>
-  <si>
-    <t>thống nhất</t>
-  </si>
-  <si>
-    <t>ld 1 năm</t>
-  </si>
-  <si>
-    <t>nghaitest</t>
+    <t>HỒ SƠ NHẬN VIỆC</t>
+  </si>
+  <si>
+    <t>NGƯỜI THAM CHIẾU</t>
+  </si>
+  <si>
+    <t>CCCD SAO Y</t>
+  </si>
+  <si>
+    <t>SYLL</t>
+  </si>
+  <si>
+    <t>ĐƠN XIN VIỆC</t>
+  </si>
+  <si>
+    <t>SCAN</t>
+  </si>
+  <si>
+    <t>HỌ VÀ TÊN</t>
+  </si>
+  <si>
+    <t>MỐI QUAN HỆ</t>
+  </si>
+  <si>
+    <t>SĐT</t>
+  </si>
+  <si>
+    <t>ĐỊA CHỈ</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Trạng thái</t>
+  </si>
+  <si>
+    <t>Làm việc</t>
   </si>
 </sst>
 </file>
@@ -989,7 +956,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\/mm\/yyyy"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1042,8 +1009,22 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1146,8 +1127,14 @@
         <bgColor rgb="FFFBE4D5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1233,11 +1220,76 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1249,9 +1301,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1305,7 +1354,6 @@
     <xf numFmtId="49" fontId="1" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1371,6 +1419,31 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1699,318 +1772,263 @@
     <col min="25" max="25" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="32" max="33" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="20.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" s="6" customFormat="1" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:52" s="5" customFormat="1" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="35"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" s="40"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+      <c r="U1" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1" s="23"/>
+      <c r="W1" s="23"/>
+      <c r="X1" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y1" s="25"/>
+      <c r="Z1" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA1" s="25"/>
+      <c r="AB1" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC1" s="28"/>
+      <c r="AD1" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE1" s="28"/>
+      <c r="AF1" s="28"/>
+      <c r="AG1" s="28"/>
+      <c r="AH1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM1" s="44" t="s">
+        <v>48</v>
+      </c>
+      <c r="AN1" s="45"/>
+      <c r="AO1" s="45"/>
+      <c r="AP1" s="46"/>
+      <c r="AQ1" s="47" t="s">
+        <v>49</v>
+      </c>
+      <c r="AR1" s="47"/>
+      <c r="AS1" s="47"/>
+      <c r="AT1" s="47"/>
+      <c r="AU1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AV1" s="4"/>
+      <c r="AW1" s="4"/>
+      <c r="AX1" s="4"/>
+      <c r="AY1" s="4"/>
+      <c r="AZ1" s="4"/>
+    </row>
+    <row r="2" spans="1:52" s="5" customFormat="1" ht="115.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="33"/>
+      <c r="B2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="36" t="s">
+      <c r="G2" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="37"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="39" t="s">
+      <c r="H2" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="24" t="s">
+      <c r="I2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M1" s="42"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="44" t="s">
+      <c r="J2" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="32" t="s">
+      <c r="K2" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="R1" s="33"/>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="24" t="s">
+      <c r="L2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="26" t="s">
+      <c r="M2" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="Y1" s="27"/>
-      <c r="Z1" s="28" t="s">
+      <c r="N2" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="AA1" s="27"/>
-      <c r="AB1" s="29" t="s">
+      <c r="O2" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="AC1" s="30"/>
-      <c r="AD1" s="31" t="s">
+      <c r="P2" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="AE1" s="30"/>
-      <c r="AF1" s="30"/>
-      <c r="AG1" s="30"/>
-      <c r="AH1" s="2" t="s">
+      <c r="Q2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="R2" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="S2" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="T2" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="U2" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="5"/>
-      <c r="AO1" s="5"/>
-      <c r="AP1" s="5"/>
-      <c r="AQ1" s="5"/>
-      <c r="AR1" s="5"/>
-      <c r="AS1" s="5"/>
-      <c r="AT1" s="5"/>
-      <c r="AU1" s="5"/>
-      <c r="AV1" s="5"/>
-      <c r="AW1" s="5"/>
-      <c r="AX1" s="5"/>
-      <c r="AY1" s="5"/>
-      <c r="AZ1" s="5"/>
-    </row>
-    <row r="2" spans="1:52" s="6" customFormat="1" ht="115.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="35"/>
-      <c r="B2" s="7" t="s">
+      <c r="V2" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="W2" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="X2" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="Y2" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="Z2" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="AA2" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="AB2" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="AC2" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="AD2" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="AE2" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="AF2" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="AG2" s="21" t="s">
         <v>47</v>
-      </c>
-      <c r="N2" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="O2" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="P2" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q2" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="R2" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="S2" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="T2" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="U2" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="V2" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="W2" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="X2" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y2" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z2" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA2" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB2" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="AC2" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD2" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE2" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="AF2" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="AG2" s="22" t="s">
-        <v>67</v>
       </c>
       <c r="AH2" s="2"/>
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
       <c r="AL2" s="3"/>
-      <c r="AM2" s="4"/>
-      <c r="AN2" s="4"/>
-      <c r="AO2" s="4"/>
-      <c r="AP2" s="4"/>
-      <c r="AQ2" s="5"/>
-      <c r="AR2" s="5"/>
-      <c r="AS2" s="5"/>
-      <c r="AT2" s="5"/>
-      <c r="AU2" s="5"/>
-      <c r="AV2" s="5"/>
-      <c r="AW2" s="5"/>
-      <c r="AX2" s="5"/>
-      <c r="AY2" s="5"/>
-      <c r="AZ2" s="5"/>
+      <c r="AM2" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN2" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="AO2" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="AP2" s="48" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ2" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="AR2" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="AS2" s="49" t="s">
+        <v>56</v>
+      </c>
+      <c r="AT2" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="AU2" s="4"/>
+      <c r="AV2" s="4"/>
+      <c r="AW2" s="4"/>
+      <c r="AX2" s="4"/>
+      <c r="AY2" s="4"/>
+      <c r="AZ2" s="4"/>
     </row>
-    <row r="3" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" t="s">
-        <v>0</v>
-      </c>
-      <c r="I3" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" t="s">
-        <v>2</v>
-      </c>
-      <c r="K3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>100000000002</v>
-      </c>
-      <c r="M3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N3" t="s">
-        <v>0</v>
-      </c>
-      <c r="O3" t="s">
-        <v>13</v>
-      </c>
-      <c r="P3" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>15</v>
-      </c>
-      <c r="R3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S3" t="s">
-        <v>17</v>
-      </c>
-      <c r="T3">
-        <v>900001002</v>
-      </c>
-      <c r="U3" t="s">
-        <v>6</v>
-      </c>
-      <c r="V3" t="s">
-        <v>18</v>
-      </c>
-      <c r="W3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X3" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y3" s="23">
-        <v>45953</v>
-      </c>
-      <c r="Z3">
-        <v>1</v>
-      </c>
-      <c r="AA3" s="23">
-        <v>44127</v>
-      </c>
-      <c r="AB3">
-        <v>123</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD3">
-        <v>1</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF3" s="23">
-        <v>45219</v>
-      </c>
-      <c r="AG3" s="23">
-        <v>45585</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>71</v>
+    <row r="3" spans="1:52" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM3" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="AN3" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="AO3" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="AP3" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="AQ3" s="51"/>
+      <c r="AR3" s="51"/>
+      <c r="AS3" s="52"/>
+      <c r="AT3" s="51"/>
+      <c r="AU3" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="13">
+    <mergeCell ref="AM1:AP1"/>
+    <mergeCell ref="AQ1:AT1"/>
     <mergeCell ref="Q1:T1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:E1"/>
